--- a/public/importacao_pessoas.xlsx
+++ b/public/importacao_pessoas.xlsx
@@ -1,103 +1,66 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="500" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10">
   <si>
-    <t xml:space="preserve">nome</t>
+    <t>nome</t>
   </si>
   <si>
-    <t xml:space="preserve">cpf</t>
+    <t>cpf</t>
   </si>
   <si>
-    <t xml:space="preserve">email</t>
+    <t>email</t>
   </si>
   <si>
-    <t xml:space="preserve">data_admissao</t>
+    <t>data_admissao</t>
   </si>
   <si>
-    <t xml:space="preserve">telefone</t>
+    <t>telefone</t>
   </si>
   <si>
-    <t xml:space="preserve">registro_funcional</t>
+    <t>registro_funcional</t>
   </si>
   <si>
-    <t xml:space="preserve">cod_cargo</t>
+    <t>cod_cargo</t>
   </si>
   <si>
-    <t xml:space="preserve">responsavel</t>
+    <t>responsavel</t>
   </si>
   <si>
-    <t xml:space="preserve">status</t>
+    <t>status</t>
+  </si>
+  <si>
+    <t>cpf_lider</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -109,7 +72,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -117,45 +80,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="true">
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="true">
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -394,65 +334,3355 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J1000"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.5390625" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.14"/>
+    <col min="2" max="2" width="9.10" customWidth="true" style="0"/>
+    <col min="4" max="4" width="13.89" customWidth="true" style="0"/>
+    <col min="6" max="6" width="17.43" customWidth="true" style="0"/>
+    <col min="7" max="7" width="9.85" customWidth="true" style="0"/>
+    <col min="8" max="8" width="12.14" customWidth="true" style="0"/>
+    <col min="10" max="10" width="15" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:10" customHeight="1" ht="13.8">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="0" t="n">
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" customHeight="1" ht="13.8">
+      <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2">
         <v>1</v>
       </c>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="J39" s="1"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="J40" s="1"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="J45" s="1"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="J46" s="1"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="J47" s="1"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="J48" s="1"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="J49" s="1"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="J50" s="1"/>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="J51" s="1"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="J58" s="1"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="J59" s="1"/>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="J60" s="1"/>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="J61" s="1"/>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="J62" s="1"/>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="J63" s="1"/>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="J64" s="1"/>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="J65" s="1"/>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="J66" s="1"/>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="J67" s="1"/>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="J68" s="1"/>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="J69" s="1"/>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="J70" s="1"/>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="J71" s="1"/>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="J72" s="1"/>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="J73" s="1"/>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="J74" s="1"/>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="J75" s="1"/>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="J76" s="1"/>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="J77" s="1"/>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="J78" s="1"/>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="J79" s="1"/>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="J80" s="1"/>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="J81" s="1"/>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="J82" s="1"/>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="J83" s="1"/>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="J84" s="1"/>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="J85" s="1"/>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="J86" s="1"/>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="J87" s="1"/>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="J88" s="1"/>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="J89" s="1"/>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="J90" s="1"/>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="J91" s="1"/>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="J92" s="1"/>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="J93" s="1"/>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="J94" s="1"/>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="J95" s="1"/>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="J96" s="1"/>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="J97" s="1"/>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="J98" s="1"/>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="J99" s="1"/>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="J100" s="1"/>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="J101" s="1"/>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="J102" s="1"/>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="J103" s="1"/>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="J104" s="1"/>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="J105" s="1"/>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="J106" s="1"/>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="J107" s="1"/>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="J108" s="1"/>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="J109" s="1"/>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="J110" s="1"/>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="J111" s="1"/>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="J112" s="1"/>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="J113" s="1"/>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="J114" s="1"/>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="J115" s="1"/>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="J116" s="1"/>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="J117" s="1"/>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="J118" s="1"/>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="J119" s="1"/>
+    </row>
+    <row r="120" spans="1:10">
+      <c r="J120" s="1"/>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="J121" s="1"/>
+    </row>
+    <row r="122" spans="1:10">
+      <c r="J122" s="1"/>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="J123" s="1"/>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="J124" s="1"/>
+    </row>
+    <row r="125" spans="1:10">
+      <c r="J125" s="1"/>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="J126" s="1"/>
+    </row>
+    <row r="127" spans="1:10">
+      <c r="J127" s="1"/>
+    </row>
+    <row r="128" spans="1:10">
+      <c r="J128" s="1"/>
+    </row>
+    <row r="129" spans="1:10">
+      <c r="J129" s="1"/>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="J130" s="1"/>
+    </row>
+    <row r="131" spans="1:10">
+      <c r="J131" s="1"/>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="J132" s="1"/>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="J133" s="1"/>
+    </row>
+    <row r="134" spans="1:10">
+      <c r="J134" s="1"/>
+    </row>
+    <row r="135" spans="1:10">
+      <c r="J135" s="1"/>
+    </row>
+    <row r="136" spans="1:10">
+      <c r="J136" s="1"/>
+    </row>
+    <row r="137" spans="1:10">
+      <c r="J137" s="1"/>
+    </row>
+    <row r="138" spans="1:10">
+      <c r="J138" s="1"/>
+    </row>
+    <row r="139" spans="1:10">
+      <c r="J139" s="1"/>
+    </row>
+    <row r="140" spans="1:10">
+      <c r="J140" s="1"/>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="J141" s="1"/>
+    </row>
+    <row r="142" spans="1:10">
+      <c r="J142" s="1"/>
+    </row>
+    <row r="143" spans="1:10">
+      <c r="J143" s="1"/>
+    </row>
+    <row r="144" spans="1:10">
+      <c r="J144" s="1"/>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="J145" s="1"/>
+    </row>
+    <row r="146" spans="1:10">
+      <c r="J146" s="1"/>
+    </row>
+    <row r="147" spans="1:10">
+      <c r="J147" s="1"/>
+    </row>
+    <row r="148" spans="1:10">
+      <c r="J148" s="1"/>
+    </row>
+    <row r="149" spans="1:10">
+      <c r="J149" s="1"/>
+    </row>
+    <row r="150" spans="1:10">
+      <c r="J150" s="1"/>
+    </row>
+    <row r="151" spans="1:10">
+      <c r="J151" s="1"/>
+    </row>
+    <row r="152" spans="1:10">
+      <c r="J152" s="1"/>
+    </row>
+    <row r="153" spans="1:10">
+      <c r="J153" s="1"/>
+    </row>
+    <row r="154" spans="1:10">
+      <c r="J154" s="1"/>
+    </row>
+    <row r="155" spans="1:10">
+      <c r="J155" s="1"/>
+    </row>
+    <row r="156" spans="1:10">
+      <c r="J156" s="1"/>
+    </row>
+    <row r="157" spans="1:10">
+      <c r="J157" s="1"/>
+    </row>
+    <row r="158" spans="1:10">
+      <c r="J158" s="1"/>
+    </row>
+    <row r="159" spans="1:10">
+      <c r="J159" s="1"/>
+    </row>
+    <row r="160" spans="1:10">
+      <c r="J160" s="1"/>
+    </row>
+    <row r="161" spans="1:10">
+      <c r="J161" s="1"/>
+    </row>
+    <row r="162" spans="1:10">
+      <c r="J162" s="1"/>
+    </row>
+    <row r="163" spans="1:10">
+      <c r="J163" s="1"/>
+    </row>
+    <row r="164" spans="1:10">
+      <c r="J164" s="1"/>
+    </row>
+    <row r="165" spans="1:10">
+      <c r="J165" s="1"/>
+    </row>
+    <row r="166" spans="1:10">
+      <c r="J166" s="1"/>
+    </row>
+    <row r="167" spans="1:10">
+      <c r="J167" s="1"/>
+    </row>
+    <row r="168" spans="1:10">
+      <c r="J168" s="1"/>
+    </row>
+    <row r="169" spans="1:10">
+      <c r="J169" s="1"/>
+    </row>
+    <row r="170" spans="1:10">
+      <c r="J170" s="1"/>
+    </row>
+    <row r="171" spans="1:10">
+      <c r="J171" s="1"/>
+    </row>
+    <row r="172" spans="1:10">
+      <c r="J172" s="1"/>
+    </row>
+    <row r="173" spans="1:10">
+      <c r="J173" s="1"/>
+    </row>
+    <row r="174" spans="1:10">
+      <c r="J174" s="1"/>
+    </row>
+    <row r="175" spans="1:10">
+      <c r="J175" s="1"/>
+    </row>
+    <row r="176" spans="1:10">
+      <c r="J176" s="1"/>
+    </row>
+    <row r="177" spans="1:10">
+      <c r="J177" s="1"/>
+    </row>
+    <row r="178" spans="1:10">
+      <c r="J178" s="1"/>
+    </row>
+    <row r="179" spans="1:10">
+      <c r="J179" s="1"/>
+    </row>
+    <row r="180" spans="1:10">
+      <c r="J180" s="1"/>
+    </row>
+    <row r="181" spans="1:10">
+      <c r="J181" s="1"/>
+    </row>
+    <row r="182" spans="1:10">
+      <c r="J182" s="1"/>
+    </row>
+    <row r="183" spans="1:10">
+      <c r="J183" s="1"/>
+    </row>
+    <row r="184" spans="1:10">
+      <c r="J184" s="1"/>
+    </row>
+    <row r="185" spans="1:10">
+      <c r="J185" s="1"/>
+    </row>
+    <row r="186" spans="1:10">
+      <c r="J186" s="1"/>
+    </row>
+    <row r="187" spans="1:10">
+      <c r="J187" s="1"/>
+    </row>
+    <row r="188" spans="1:10">
+      <c r="J188" s="1"/>
+    </row>
+    <row r="189" spans="1:10">
+      <c r="J189" s="1"/>
+    </row>
+    <row r="190" spans="1:10">
+      <c r="J190" s="1"/>
+    </row>
+    <row r="191" spans="1:10">
+      <c r="J191" s="1"/>
+    </row>
+    <row r="192" spans="1:10">
+      <c r="J192" s="1"/>
+    </row>
+    <row r="193" spans="1:10">
+      <c r="J193" s="1"/>
+    </row>
+    <row r="194" spans="1:10">
+      <c r="J194" s="1"/>
+    </row>
+    <row r="195" spans="1:10">
+      <c r="J195" s="1"/>
+    </row>
+    <row r="196" spans="1:10">
+      <c r="J196" s="1"/>
+    </row>
+    <row r="197" spans="1:10">
+      <c r="J197" s="1"/>
+    </row>
+    <row r="198" spans="1:10">
+      <c r="J198" s="1"/>
+    </row>
+    <row r="199" spans="1:10">
+      <c r="J199" s="1"/>
+    </row>
+    <row r="200" spans="1:10">
+      <c r="J200" s="1"/>
+    </row>
+    <row r="201" spans="1:10">
+      <c r="J201" s="1"/>
+    </row>
+    <row r="202" spans="1:10">
+      <c r="J202" s="1"/>
+    </row>
+    <row r="203" spans="1:10">
+      <c r="J203" s="1"/>
+    </row>
+    <row r="204" spans="1:10">
+      <c r="J204" s="1"/>
+    </row>
+    <row r="205" spans="1:10">
+      <c r="J205" s="1"/>
+    </row>
+    <row r="206" spans="1:10">
+      <c r="J206" s="1"/>
+    </row>
+    <row r="207" spans="1:10">
+      <c r="J207" s="1"/>
+    </row>
+    <row r="208" spans="1:10">
+      <c r="J208" s="1"/>
+    </row>
+    <row r="209" spans="1:10">
+      <c r="J209" s="1"/>
+    </row>
+    <row r="210" spans="1:10">
+      <c r="J210" s="1"/>
+    </row>
+    <row r="211" spans="1:10">
+      <c r="J211" s="1"/>
+    </row>
+    <row r="212" spans="1:10">
+      <c r="J212" s="1"/>
+    </row>
+    <row r="213" spans="1:10">
+      <c r="J213" s="1"/>
+    </row>
+    <row r="214" spans="1:10">
+      <c r="J214" s="1"/>
+    </row>
+    <row r="215" spans="1:10">
+      <c r="J215" s="1"/>
+    </row>
+    <row r="216" spans="1:10">
+      <c r="J216" s="1"/>
+    </row>
+    <row r="217" spans="1:10">
+      <c r="J217" s="1"/>
+    </row>
+    <row r="218" spans="1:10">
+      <c r="J218" s="1"/>
+    </row>
+    <row r="219" spans="1:10">
+      <c r="J219" s="1"/>
+    </row>
+    <row r="220" spans="1:10">
+      <c r="J220" s="1"/>
+    </row>
+    <row r="221" spans="1:10">
+      <c r="J221" s="1"/>
+    </row>
+    <row r="222" spans="1:10">
+      <c r="J222" s="1"/>
+    </row>
+    <row r="223" spans="1:10">
+      <c r="J223" s="1"/>
+    </row>
+    <row r="224" spans="1:10">
+      <c r="J224" s="1"/>
+    </row>
+    <row r="225" spans="1:10">
+      <c r="J225" s="1"/>
+    </row>
+    <row r="226" spans="1:10">
+      <c r="J226" s="1"/>
+    </row>
+    <row r="227" spans="1:10">
+      <c r="J227" s="1"/>
+    </row>
+    <row r="228" spans="1:10">
+      <c r="J228" s="1"/>
+    </row>
+    <row r="229" spans="1:10">
+      <c r="J229" s="1"/>
+    </row>
+    <row r="230" spans="1:10">
+      <c r="J230" s="1"/>
+    </row>
+    <row r="231" spans="1:10">
+      <c r="J231" s="1"/>
+    </row>
+    <row r="232" spans="1:10">
+      <c r="J232" s="1"/>
+    </row>
+    <row r="233" spans="1:10">
+      <c r="J233" s="1"/>
+    </row>
+    <row r="234" spans="1:10">
+      <c r="J234" s="1"/>
+    </row>
+    <row r="235" spans="1:10">
+      <c r="J235" s="1"/>
+    </row>
+    <row r="236" spans="1:10">
+      <c r="J236" s="1"/>
+    </row>
+    <row r="237" spans="1:10">
+      <c r="J237" s="1"/>
+    </row>
+    <row r="238" spans="1:10">
+      <c r="J238" s="1"/>
+    </row>
+    <row r="239" spans="1:10">
+      <c r="J239" s="1"/>
+    </row>
+    <row r="240" spans="1:10">
+      <c r="J240" s="1"/>
+    </row>
+    <row r="241" spans="1:10">
+      <c r="J241" s="1"/>
+    </row>
+    <row r="242" spans="1:10">
+      <c r="J242" s="1"/>
+    </row>
+    <row r="243" spans="1:10">
+      <c r="J243" s="1"/>
+    </row>
+    <row r="244" spans="1:10">
+      <c r="J244" s="1"/>
+    </row>
+    <row r="245" spans="1:10">
+      <c r="J245" s="1"/>
+    </row>
+    <row r="246" spans="1:10">
+      <c r="J246" s="1"/>
+    </row>
+    <row r="247" spans="1:10">
+      <c r="J247" s="1"/>
+    </row>
+    <row r="248" spans="1:10">
+      <c r="J248" s="1"/>
+    </row>
+    <row r="249" spans="1:10">
+      <c r="J249" s="1"/>
+    </row>
+    <row r="250" spans="1:10">
+      <c r="J250" s="1"/>
+    </row>
+    <row r="251" spans="1:10">
+      <c r="J251" s="1"/>
+    </row>
+    <row r="252" spans="1:10">
+      <c r="J252" s="1"/>
+    </row>
+    <row r="253" spans="1:10">
+      <c r="J253" s="1"/>
+    </row>
+    <row r="254" spans="1:10">
+      <c r="J254" s="1"/>
+    </row>
+    <row r="255" spans="1:10">
+      <c r="J255" s="1"/>
+    </row>
+    <row r="256" spans="1:10">
+      <c r="J256" s="1"/>
+    </row>
+    <row r="257" spans="1:10">
+      <c r="J257" s="1"/>
+    </row>
+    <row r="258" spans="1:10">
+      <c r="J258" s="1"/>
+    </row>
+    <row r="259" spans="1:10">
+      <c r="J259" s="1"/>
+    </row>
+    <row r="260" spans="1:10">
+      <c r="J260" s="1"/>
+    </row>
+    <row r="261" spans="1:10">
+      <c r="J261" s="1"/>
+    </row>
+    <row r="262" spans="1:10">
+      <c r="J262" s="1"/>
+    </row>
+    <row r="263" spans="1:10">
+      <c r="J263" s="1"/>
+    </row>
+    <row r="264" spans="1:10">
+      <c r="J264" s="1"/>
+    </row>
+    <row r="265" spans="1:10">
+      <c r="J265" s="1"/>
+    </row>
+    <row r="266" spans="1:10">
+      <c r="J266" s="1"/>
+    </row>
+    <row r="267" spans="1:10">
+      <c r="J267" s="1"/>
+    </row>
+    <row r="268" spans="1:10">
+      <c r="J268" s="1"/>
+    </row>
+    <row r="269" spans="1:10">
+      <c r="J269" s="1"/>
+    </row>
+    <row r="270" spans="1:10">
+      <c r="J270" s="1"/>
+    </row>
+    <row r="271" spans="1:10">
+      <c r="J271" s="1"/>
+    </row>
+    <row r="272" spans="1:10">
+      <c r="J272" s="1"/>
+    </row>
+    <row r="273" spans="1:10">
+      <c r="J273" s="1"/>
+    </row>
+    <row r="274" spans="1:10">
+      <c r="J274" s="1"/>
+    </row>
+    <row r="275" spans="1:10">
+      <c r="J275" s="1"/>
+    </row>
+    <row r="276" spans="1:10">
+      <c r="J276" s="1"/>
+    </row>
+    <row r="277" spans="1:10">
+      <c r="J277" s="1"/>
+    </row>
+    <row r="278" spans="1:10">
+      <c r="J278" s="1"/>
+    </row>
+    <row r="279" spans="1:10">
+      <c r="J279" s="1"/>
+    </row>
+    <row r="280" spans="1:10">
+      <c r="J280" s="1"/>
+    </row>
+    <row r="281" spans="1:10">
+      <c r="J281" s="1"/>
+    </row>
+    <row r="282" spans="1:10">
+      <c r="J282" s="1"/>
+    </row>
+    <row r="283" spans="1:10">
+      <c r="J283" s="1"/>
+    </row>
+    <row r="284" spans="1:10">
+      <c r="J284" s="1"/>
+    </row>
+    <row r="285" spans="1:10">
+      <c r="J285" s="1"/>
+    </row>
+    <row r="286" spans="1:10">
+      <c r="J286" s="1"/>
+    </row>
+    <row r="287" spans="1:10">
+      <c r="J287" s="1"/>
+    </row>
+    <row r="288" spans="1:10">
+      <c r="J288" s="1"/>
+    </row>
+    <row r="289" spans="1:10">
+      <c r="J289" s="1"/>
+    </row>
+    <row r="290" spans="1:10">
+      <c r="J290" s="1"/>
+    </row>
+    <row r="291" spans="1:10">
+      <c r="J291" s="1"/>
+    </row>
+    <row r="292" spans="1:10">
+      <c r="J292" s="1"/>
+    </row>
+    <row r="293" spans="1:10">
+      <c r="J293" s="1"/>
+    </row>
+    <row r="294" spans="1:10">
+      <c r="J294" s="1"/>
+    </row>
+    <row r="295" spans="1:10">
+      <c r="J295" s="1"/>
+    </row>
+    <row r="296" spans="1:10">
+      <c r="J296" s="1"/>
+    </row>
+    <row r="297" spans="1:10">
+      <c r="J297" s="1"/>
+    </row>
+    <row r="298" spans="1:10">
+      <c r="J298" s="1"/>
+    </row>
+    <row r="299" spans="1:10">
+      <c r="J299" s="1"/>
+    </row>
+    <row r="300" spans="1:10">
+      <c r="J300" s="1"/>
+    </row>
+    <row r="301" spans="1:10">
+      <c r="J301" s="1"/>
+    </row>
+    <row r="302" spans="1:10">
+      <c r="J302" s="1"/>
+    </row>
+    <row r="303" spans="1:10">
+      <c r="J303" s="1"/>
+    </row>
+    <row r="304" spans="1:10">
+      <c r="J304" s="1"/>
+    </row>
+    <row r="305" spans="1:10">
+      <c r="J305" s="1"/>
+    </row>
+    <row r="306" spans="1:10">
+      <c r="J306" s="1"/>
+    </row>
+    <row r="307" spans="1:10">
+      <c r="J307" s="1"/>
+    </row>
+    <row r="308" spans="1:10">
+      <c r="J308" s="1"/>
+    </row>
+    <row r="309" spans="1:10">
+      <c r="J309" s="1"/>
+    </row>
+    <row r="310" spans="1:10">
+      <c r="J310" s="1"/>
+    </row>
+    <row r="311" spans="1:10">
+      <c r="J311" s="1"/>
+    </row>
+    <row r="312" spans="1:10">
+      <c r="J312" s="1"/>
+    </row>
+    <row r="313" spans="1:10">
+      <c r="J313" s="1"/>
+    </row>
+    <row r="314" spans="1:10">
+      <c r="J314" s="1"/>
+    </row>
+    <row r="315" spans="1:10">
+      <c r="J315" s="1"/>
+    </row>
+    <row r="316" spans="1:10">
+      <c r="J316" s="1"/>
+    </row>
+    <row r="317" spans="1:10">
+      <c r="J317" s="1"/>
+    </row>
+    <row r="318" spans="1:10">
+      <c r="J318" s="1"/>
+    </row>
+    <row r="319" spans="1:10">
+      <c r="J319" s="1"/>
+    </row>
+    <row r="320" spans="1:10">
+      <c r="J320" s="1"/>
+    </row>
+    <row r="321" spans="1:10">
+      <c r="J321" s="1"/>
+    </row>
+    <row r="322" spans="1:10">
+      <c r="J322" s="1"/>
+    </row>
+    <row r="323" spans="1:10">
+      <c r="J323" s="1"/>
+    </row>
+    <row r="324" spans="1:10">
+      <c r="J324" s="1"/>
+    </row>
+    <row r="325" spans="1:10">
+      <c r="J325" s="1"/>
+    </row>
+    <row r="326" spans="1:10">
+      <c r="J326" s="1"/>
+    </row>
+    <row r="327" spans="1:10">
+      <c r="J327" s="1"/>
+    </row>
+    <row r="328" spans="1:10">
+      <c r="J328" s="1"/>
+    </row>
+    <row r="329" spans="1:10">
+      <c r="J329" s="1"/>
+    </row>
+    <row r="330" spans="1:10">
+      <c r="J330" s="1"/>
+    </row>
+    <row r="331" spans="1:10">
+      <c r="J331" s="1"/>
+    </row>
+    <row r="332" spans="1:10">
+      <c r="J332" s="1"/>
+    </row>
+    <row r="333" spans="1:10">
+      <c r="J333" s="1"/>
+    </row>
+    <row r="334" spans="1:10">
+      <c r="J334" s="1"/>
+    </row>
+    <row r="335" spans="1:10">
+      <c r="J335" s="1"/>
+    </row>
+    <row r="336" spans="1:10">
+      <c r="J336" s="1"/>
+    </row>
+    <row r="337" spans="1:10">
+      <c r="J337" s="1"/>
+    </row>
+    <row r="338" spans="1:10">
+      <c r="J338" s="1"/>
+    </row>
+    <row r="339" spans="1:10">
+      <c r="J339" s="1"/>
+    </row>
+    <row r="340" spans="1:10">
+      <c r="J340" s="1"/>
+    </row>
+    <row r="341" spans="1:10">
+      <c r="J341" s="1"/>
+    </row>
+    <row r="342" spans="1:10">
+      <c r="J342" s="1"/>
+    </row>
+    <row r="343" spans="1:10">
+      <c r="J343" s="1"/>
+    </row>
+    <row r="344" spans="1:10">
+      <c r="J344" s="1"/>
+    </row>
+    <row r="345" spans="1:10">
+      <c r="J345" s="1"/>
+    </row>
+    <row r="346" spans="1:10">
+      <c r="J346" s="1"/>
+    </row>
+    <row r="347" spans="1:10">
+      <c r="J347" s="1"/>
+    </row>
+    <row r="348" spans="1:10">
+      <c r="J348" s="1"/>
+    </row>
+    <row r="349" spans="1:10">
+      <c r="J349" s="1"/>
+    </row>
+    <row r="350" spans="1:10">
+      <c r="J350" s="1"/>
+    </row>
+    <row r="351" spans="1:10">
+      <c r="J351" s="1"/>
+    </row>
+    <row r="352" spans="1:10">
+      <c r="J352" s="1"/>
+    </row>
+    <row r="353" spans="1:10">
+      <c r="J353" s="1"/>
+    </row>
+    <row r="354" spans="1:10">
+      <c r="J354" s="1"/>
+    </row>
+    <row r="355" spans="1:10">
+      <c r="J355" s="1"/>
+    </row>
+    <row r="356" spans="1:10">
+      <c r="J356" s="1"/>
+    </row>
+    <row r="357" spans="1:10">
+      <c r="J357" s="1"/>
+    </row>
+    <row r="358" spans="1:10">
+      <c r="J358" s="1"/>
+    </row>
+    <row r="359" spans="1:10">
+      <c r="J359" s="1"/>
+    </row>
+    <row r="360" spans="1:10">
+      <c r="J360" s="1"/>
+    </row>
+    <row r="361" spans="1:10">
+      <c r="J361" s="1"/>
+    </row>
+    <row r="362" spans="1:10">
+      <c r="J362" s="1"/>
+    </row>
+    <row r="363" spans="1:10">
+      <c r="J363" s="1"/>
+    </row>
+    <row r="364" spans="1:10">
+      <c r="J364" s="1"/>
+    </row>
+    <row r="365" spans="1:10">
+      <c r="J365" s="1"/>
+    </row>
+    <row r="366" spans="1:10">
+      <c r="J366" s="1"/>
+    </row>
+    <row r="367" spans="1:10">
+      <c r="J367" s="1"/>
+    </row>
+    <row r="368" spans="1:10">
+      <c r="J368" s="1"/>
+    </row>
+    <row r="369" spans="1:10">
+      <c r="J369" s="1"/>
+    </row>
+    <row r="370" spans="1:10">
+      <c r="J370" s="1"/>
+    </row>
+    <row r="371" spans="1:10">
+      <c r="J371" s="1"/>
+    </row>
+    <row r="372" spans="1:10">
+      <c r="J372" s="1"/>
+    </row>
+    <row r="373" spans="1:10">
+      <c r="J373" s="1"/>
+    </row>
+    <row r="374" spans="1:10">
+      <c r="J374" s="1"/>
+    </row>
+    <row r="375" spans="1:10">
+      <c r="J375" s="1"/>
+    </row>
+    <row r="376" spans="1:10">
+      <c r="J376" s="1"/>
+    </row>
+    <row r="377" spans="1:10">
+      <c r="J377" s="1"/>
+    </row>
+    <row r="378" spans="1:10">
+      <c r="J378" s="1"/>
+    </row>
+    <row r="379" spans="1:10">
+      <c r="J379" s="1"/>
+    </row>
+    <row r="380" spans="1:10">
+      <c r="J380" s="1"/>
+    </row>
+    <row r="381" spans="1:10">
+      <c r="J381" s="1"/>
+    </row>
+    <row r="382" spans="1:10">
+      <c r="J382" s="1"/>
+    </row>
+    <row r="383" spans="1:10">
+      <c r="J383" s="1"/>
+    </row>
+    <row r="384" spans="1:10">
+      <c r="J384" s="1"/>
+    </row>
+    <row r="385" spans="1:10">
+      <c r="J385" s="1"/>
+    </row>
+    <row r="386" spans="1:10">
+      <c r="J386" s="1"/>
+    </row>
+    <row r="387" spans="1:10">
+      <c r="J387" s="1"/>
+    </row>
+    <row r="388" spans="1:10">
+      <c r="J388" s="1"/>
+    </row>
+    <row r="389" spans="1:10">
+      <c r="J389" s="1"/>
+    </row>
+    <row r="390" spans="1:10">
+      <c r="J390" s="1"/>
+    </row>
+    <row r="391" spans="1:10">
+      <c r="J391" s="1"/>
+    </row>
+    <row r="392" spans="1:10">
+      <c r="J392" s="1"/>
+    </row>
+    <row r="393" spans="1:10">
+      <c r="J393" s="1"/>
+    </row>
+    <row r="394" spans="1:10">
+      <c r="J394" s="1"/>
+    </row>
+    <row r="395" spans="1:10">
+      <c r="J395" s="1"/>
+    </row>
+    <row r="396" spans="1:10">
+      <c r="J396" s="1"/>
+    </row>
+    <row r="397" spans="1:10">
+      <c r="J397" s="1"/>
+    </row>
+    <row r="398" spans="1:10">
+      <c r="J398" s="1"/>
+    </row>
+    <row r="399" spans="1:10">
+      <c r="J399" s="1"/>
+    </row>
+    <row r="400" spans="1:10">
+      <c r="J400" s="1"/>
+    </row>
+    <row r="401" spans="1:10">
+      <c r="J401" s="1"/>
+    </row>
+    <row r="402" spans="1:10">
+      <c r="J402" s="1"/>
+    </row>
+    <row r="403" spans="1:10">
+      <c r="J403" s="1"/>
+    </row>
+    <row r="404" spans="1:10">
+      <c r="J404" s="1"/>
+    </row>
+    <row r="405" spans="1:10">
+      <c r="J405" s="1"/>
+    </row>
+    <row r="406" spans="1:10">
+      <c r="J406" s="1"/>
+    </row>
+    <row r="407" spans="1:10">
+      <c r="J407" s="1"/>
+    </row>
+    <row r="408" spans="1:10">
+      <c r="J408" s="1"/>
+    </row>
+    <row r="409" spans="1:10">
+      <c r="J409" s="1"/>
+    </row>
+    <row r="410" spans="1:10">
+      <c r="J410" s="1"/>
+    </row>
+    <row r="411" spans="1:10">
+      <c r="J411" s="1"/>
+    </row>
+    <row r="412" spans="1:10">
+      <c r="J412" s="1"/>
+    </row>
+    <row r="413" spans="1:10">
+      <c r="J413" s="1"/>
+    </row>
+    <row r="414" spans="1:10">
+      <c r="J414" s="1"/>
+    </row>
+    <row r="415" spans="1:10">
+      <c r="J415" s="1"/>
+    </row>
+    <row r="416" spans="1:10">
+      <c r="J416" s="1"/>
+    </row>
+    <row r="417" spans="1:10">
+      <c r="J417" s="1"/>
+    </row>
+    <row r="418" spans="1:10">
+      <c r="J418" s="1"/>
+    </row>
+    <row r="419" spans="1:10">
+      <c r="J419" s="1"/>
+    </row>
+    <row r="420" spans="1:10">
+      <c r="J420" s="1"/>
+    </row>
+    <row r="421" spans="1:10">
+      <c r="J421" s="1"/>
+    </row>
+    <row r="422" spans="1:10">
+      <c r="J422" s="1"/>
+    </row>
+    <row r="423" spans="1:10">
+      <c r="J423" s="1"/>
+    </row>
+    <row r="424" spans="1:10">
+      <c r="J424" s="1"/>
+    </row>
+    <row r="425" spans="1:10">
+      <c r="J425" s="1"/>
+    </row>
+    <row r="426" spans="1:10">
+      <c r="J426" s="1"/>
+    </row>
+    <row r="427" spans="1:10">
+      <c r="J427" s="1"/>
+    </row>
+    <row r="428" spans="1:10">
+      <c r="J428" s="1"/>
+    </row>
+    <row r="429" spans="1:10">
+      <c r="J429" s="1"/>
+    </row>
+    <row r="430" spans="1:10">
+      <c r="J430" s="1"/>
+    </row>
+    <row r="431" spans="1:10">
+      <c r="J431" s="1"/>
+    </row>
+    <row r="432" spans="1:10">
+      <c r="J432" s="1"/>
+    </row>
+    <row r="433" spans="1:10">
+      <c r="J433" s="1"/>
+    </row>
+    <row r="434" spans="1:10">
+      <c r="J434" s="1"/>
+    </row>
+    <row r="435" spans="1:10">
+      <c r="J435" s="1"/>
+    </row>
+    <row r="436" spans="1:10">
+      <c r="J436" s="1"/>
+    </row>
+    <row r="437" spans="1:10">
+      <c r="J437" s="1"/>
+    </row>
+    <row r="438" spans="1:10">
+      <c r="J438" s="1"/>
+    </row>
+    <row r="439" spans="1:10">
+      <c r="J439" s="1"/>
+    </row>
+    <row r="440" spans="1:10">
+      <c r="J440" s="1"/>
+    </row>
+    <row r="441" spans="1:10">
+      <c r="J441" s="1"/>
+    </row>
+    <row r="442" spans="1:10">
+      <c r="J442" s="1"/>
+    </row>
+    <row r="443" spans="1:10">
+      <c r="J443" s="1"/>
+    </row>
+    <row r="444" spans="1:10">
+      <c r="J444" s="1"/>
+    </row>
+    <row r="445" spans="1:10">
+      <c r="J445" s="1"/>
+    </row>
+    <row r="446" spans="1:10">
+      <c r="J446" s="1"/>
+    </row>
+    <row r="447" spans="1:10">
+      <c r="J447" s="1"/>
+    </row>
+    <row r="448" spans="1:10">
+      <c r="J448" s="1"/>
+    </row>
+    <row r="449" spans="1:10">
+      <c r="J449" s="1"/>
+    </row>
+    <row r="450" spans="1:10">
+      <c r="J450" s="1"/>
+    </row>
+    <row r="451" spans="1:10">
+      <c r="J451" s="1"/>
+    </row>
+    <row r="452" spans="1:10">
+      <c r="J452" s="1"/>
+    </row>
+    <row r="453" spans="1:10">
+      <c r="J453" s="1"/>
+    </row>
+    <row r="454" spans="1:10">
+      <c r="J454" s="1"/>
+    </row>
+    <row r="455" spans="1:10">
+      <c r="J455" s="1"/>
+    </row>
+    <row r="456" spans="1:10">
+      <c r="J456" s="1"/>
+    </row>
+    <row r="457" spans="1:10">
+      <c r="J457" s="1"/>
+    </row>
+    <row r="458" spans="1:10">
+      <c r="J458" s="1"/>
+    </row>
+    <row r="459" spans="1:10">
+      <c r="J459" s="1"/>
+    </row>
+    <row r="460" spans="1:10">
+      <c r="J460" s="1"/>
+    </row>
+    <row r="461" spans="1:10">
+      <c r="J461" s="1"/>
+    </row>
+    <row r="462" spans="1:10">
+      <c r="J462" s="1"/>
+    </row>
+    <row r="463" spans="1:10">
+      <c r="J463" s="1"/>
+    </row>
+    <row r="464" spans="1:10">
+      <c r="J464" s="1"/>
+    </row>
+    <row r="465" spans="1:10">
+      <c r="J465" s="1"/>
+    </row>
+    <row r="466" spans="1:10">
+      <c r="J466" s="1"/>
+    </row>
+    <row r="467" spans="1:10">
+      <c r="J467" s="1"/>
+    </row>
+    <row r="468" spans="1:10">
+      <c r="J468" s="1"/>
+    </row>
+    <row r="469" spans="1:10">
+      <c r="J469" s="1"/>
+    </row>
+    <row r="470" spans="1:10">
+      <c r="J470" s="1"/>
+    </row>
+    <row r="471" spans="1:10">
+      <c r="J471" s="1"/>
+    </row>
+    <row r="472" spans="1:10">
+      <c r="J472" s="1"/>
+    </row>
+    <row r="473" spans="1:10">
+      <c r="J473" s="1"/>
+    </row>
+    <row r="474" spans="1:10">
+      <c r="J474" s="1"/>
+    </row>
+    <row r="475" spans="1:10">
+      <c r="J475" s="1"/>
+    </row>
+    <row r="476" spans="1:10">
+      <c r="J476" s="1"/>
+    </row>
+    <row r="477" spans="1:10">
+      <c r="J477" s="1"/>
+    </row>
+    <row r="478" spans="1:10">
+      <c r="J478" s="1"/>
+    </row>
+    <row r="479" spans="1:10">
+      <c r="J479" s="1"/>
+    </row>
+    <row r="480" spans="1:10">
+      <c r="J480" s="1"/>
+    </row>
+    <row r="481" spans="1:10">
+      <c r="J481" s="1"/>
+    </row>
+    <row r="482" spans="1:10">
+      <c r="J482" s="1"/>
+    </row>
+    <row r="483" spans="1:10">
+      <c r="J483" s="1"/>
+    </row>
+    <row r="484" spans="1:10">
+      <c r="J484" s="1"/>
+    </row>
+    <row r="485" spans="1:10">
+      <c r="J485" s="1"/>
+    </row>
+    <row r="486" spans="1:10">
+      <c r="J486" s="1"/>
+    </row>
+    <row r="487" spans="1:10">
+      <c r="J487" s="1"/>
+    </row>
+    <row r="488" spans="1:10">
+      <c r="J488" s="1"/>
+    </row>
+    <row r="489" spans="1:10">
+      <c r="J489" s="1"/>
+    </row>
+    <row r="490" spans="1:10">
+      <c r="J490" s="1"/>
+    </row>
+    <row r="491" spans="1:10">
+      <c r="J491" s="1"/>
+    </row>
+    <row r="492" spans="1:10">
+      <c r="J492" s="1"/>
+    </row>
+    <row r="493" spans="1:10">
+      <c r="J493" s="1"/>
+    </row>
+    <row r="494" spans="1:10">
+      <c r="J494" s="1"/>
+    </row>
+    <row r="495" spans="1:10">
+      <c r="J495" s="1"/>
+    </row>
+    <row r="496" spans="1:10">
+      <c r="J496" s="1"/>
+    </row>
+    <row r="497" spans="1:10">
+      <c r="J497" s="1"/>
+    </row>
+    <row r="498" spans="1:10">
+      <c r="J498" s="1"/>
+    </row>
+    <row r="499" spans="1:10">
+      <c r="J499" s="1"/>
+    </row>
+    <row r="500" spans="1:10">
+      <c r="J500" s="1"/>
+    </row>
+    <row r="501" spans="1:10">
+      <c r="J501" s="1"/>
+    </row>
+    <row r="502" spans="1:10">
+      <c r="J502" s="1"/>
+    </row>
+    <row r="503" spans="1:10">
+      <c r="J503" s="1"/>
+    </row>
+    <row r="504" spans="1:10">
+      <c r="J504" s="1"/>
+    </row>
+    <row r="505" spans="1:10">
+      <c r="J505" s="1"/>
+    </row>
+    <row r="506" spans="1:10">
+      <c r="J506" s="1"/>
+    </row>
+    <row r="507" spans="1:10">
+      <c r="J507" s="1"/>
+    </row>
+    <row r="508" spans="1:10">
+      <c r="J508" s="1"/>
+    </row>
+    <row r="509" spans="1:10">
+      <c r="J509" s="1"/>
+    </row>
+    <row r="510" spans="1:10">
+      <c r="J510" s="1"/>
+    </row>
+    <row r="511" spans="1:10">
+      <c r="J511" s="1"/>
+    </row>
+    <row r="512" spans="1:10">
+      <c r="J512" s="1"/>
+    </row>
+    <row r="513" spans="1:10">
+      <c r="J513" s="1"/>
+    </row>
+    <row r="514" spans="1:10">
+      <c r="J514" s="1"/>
+    </row>
+    <row r="515" spans="1:10">
+      <c r="J515" s="1"/>
+    </row>
+    <row r="516" spans="1:10">
+      <c r="J516" s="1"/>
+    </row>
+    <row r="517" spans="1:10">
+      <c r="J517" s="1"/>
+    </row>
+    <row r="518" spans="1:10">
+      <c r="J518" s="1"/>
+    </row>
+    <row r="519" spans="1:10">
+      <c r="J519" s="1"/>
+    </row>
+    <row r="520" spans="1:10">
+      <c r="J520" s="1"/>
+    </row>
+    <row r="521" spans="1:10">
+      <c r="J521" s="1"/>
+    </row>
+    <row r="522" spans="1:10">
+      <c r="J522" s="1"/>
+    </row>
+    <row r="523" spans="1:10">
+      <c r="J523" s="1"/>
+    </row>
+    <row r="524" spans="1:10">
+      <c r="J524" s="1"/>
+    </row>
+    <row r="525" spans="1:10">
+      <c r="J525" s="1"/>
+    </row>
+    <row r="526" spans="1:10">
+      <c r="J526" s="1"/>
+    </row>
+    <row r="527" spans="1:10">
+      <c r="J527" s="1"/>
+    </row>
+    <row r="528" spans="1:10">
+      <c r="J528" s="1"/>
+    </row>
+    <row r="529" spans="1:10">
+      <c r="J529" s="1"/>
+    </row>
+    <row r="530" spans="1:10">
+      <c r="J530" s="1"/>
+    </row>
+    <row r="531" spans="1:10">
+      <c r="J531" s="1"/>
+    </row>
+    <row r="532" spans="1:10">
+      <c r="J532" s="1"/>
+    </row>
+    <row r="533" spans="1:10">
+      <c r="J533" s="1"/>
+    </row>
+    <row r="534" spans="1:10">
+      <c r="J534" s="1"/>
+    </row>
+    <row r="535" spans="1:10">
+      <c r="J535" s="1"/>
+    </row>
+    <row r="536" spans="1:10">
+      <c r="J536" s="1"/>
+    </row>
+    <row r="537" spans="1:10">
+      <c r="J537" s="1"/>
+    </row>
+    <row r="538" spans="1:10">
+      <c r="J538" s="1"/>
+    </row>
+    <row r="539" spans="1:10">
+      <c r="J539" s="1"/>
+    </row>
+    <row r="540" spans="1:10">
+      <c r="J540" s="1"/>
+    </row>
+    <row r="541" spans="1:10">
+      <c r="J541" s="1"/>
+    </row>
+    <row r="542" spans="1:10">
+      <c r="J542" s="1"/>
+    </row>
+    <row r="543" spans="1:10">
+      <c r="J543" s="1"/>
+    </row>
+    <row r="544" spans="1:10">
+      <c r="J544" s="1"/>
+    </row>
+    <row r="545" spans="1:10">
+      <c r="J545" s="1"/>
+    </row>
+    <row r="546" spans="1:10">
+      <c r="J546" s="1"/>
+    </row>
+    <row r="547" spans="1:10">
+      <c r="J547" s="1"/>
+    </row>
+    <row r="548" spans="1:10">
+      <c r="J548" s="1"/>
+    </row>
+    <row r="549" spans="1:10">
+      <c r="J549" s="1"/>
+    </row>
+    <row r="550" spans="1:10">
+      <c r="J550" s="1"/>
+    </row>
+    <row r="551" spans="1:10">
+      <c r="J551" s="1"/>
+    </row>
+    <row r="552" spans="1:10">
+      <c r="J552" s="1"/>
+    </row>
+    <row r="553" spans="1:10">
+      <c r="J553" s="1"/>
+    </row>
+    <row r="554" spans="1:10">
+      <c r="J554" s="1"/>
+    </row>
+    <row r="555" spans="1:10">
+      <c r="J555" s="1"/>
+    </row>
+    <row r="556" spans="1:10">
+      <c r="J556" s="1"/>
+    </row>
+    <row r="557" spans="1:10">
+      <c r="J557" s="1"/>
+    </row>
+    <row r="558" spans="1:10">
+      <c r="J558" s="1"/>
+    </row>
+    <row r="559" spans="1:10">
+      <c r="J559" s="1"/>
+    </row>
+    <row r="560" spans="1:10">
+      <c r="J560" s="1"/>
+    </row>
+    <row r="561" spans="1:10">
+      <c r="J561" s="1"/>
+    </row>
+    <row r="562" spans="1:10">
+      <c r="J562" s="1"/>
+    </row>
+    <row r="563" spans="1:10">
+      <c r="J563" s="1"/>
+    </row>
+    <row r="564" spans="1:10">
+      <c r="J564" s="1"/>
+    </row>
+    <row r="565" spans="1:10">
+      <c r="J565" s="1"/>
+    </row>
+    <row r="566" spans="1:10">
+      <c r="J566" s="1"/>
+    </row>
+    <row r="567" spans="1:10">
+      <c r="J567" s="1"/>
+    </row>
+    <row r="568" spans="1:10">
+      <c r="J568" s="1"/>
+    </row>
+    <row r="569" spans="1:10">
+      <c r="J569" s="1"/>
+    </row>
+    <row r="570" spans="1:10">
+      <c r="J570" s="1"/>
+    </row>
+    <row r="571" spans="1:10">
+      <c r="J571" s="1"/>
+    </row>
+    <row r="572" spans="1:10">
+      <c r="J572" s="1"/>
+    </row>
+    <row r="573" spans="1:10">
+      <c r="J573" s="1"/>
+    </row>
+    <row r="574" spans="1:10">
+      <c r="J574" s="1"/>
+    </row>
+    <row r="575" spans="1:10">
+      <c r="J575" s="1"/>
+    </row>
+    <row r="576" spans="1:10">
+      <c r="J576" s="1"/>
+    </row>
+    <row r="577" spans="1:10">
+      <c r="J577" s="1"/>
+    </row>
+    <row r="578" spans="1:10">
+      <c r="J578" s="1"/>
+    </row>
+    <row r="579" spans="1:10">
+      <c r="J579" s="1"/>
+    </row>
+    <row r="580" spans="1:10">
+      <c r="J580" s="1"/>
+    </row>
+    <row r="581" spans="1:10">
+      <c r="J581" s="1"/>
+    </row>
+    <row r="582" spans="1:10">
+      <c r="J582" s="1"/>
+    </row>
+    <row r="583" spans="1:10">
+      <c r="J583" s="1"/>
+    </row>
+    <row r="584" spans="1:10">
+      <c r="J584" s="1"/>
+    </row>
+    <row r="585" spans="1:10">
+      <c r="J585" s="1"/>
+    </row>
+    <row r="586" spans="1:10">
+      <c r="J586" s="1"/>
+    </row>
+    <row r="587" spans="1:10">
+      <c r="J587" s="1"/>
+    </row>
+    <row r="588" spans="1:10">
+      <c r="J588" s="1"/>
+    </row>
+    <row r="589" spans="1:10">
+      <c r="J589" s="1"/>
+    </row>
+    <row r="590" spans="1:10">
+      <c r="J590" s="1"/>
+    </row>
+    <row r="591" spans="1:10">
+      <c r="J591" s="1"/>
+    </row>
+    <row r="592" spans="1:10">
+      <c r="J592" s="1"/>
+    </row>
+    <row r="593" spans="1:10">
+      <c r="J593" s="1"/>
+    </row>
+    <row r="594" spans="1:10">
+      <c r="J594" s="1"/>
+    </row>
+    <row r="595" spans="1:10">
+      <c r="J595" s="1"/>
+    </row>
+    <row r="596" spans="1:10">
+      <c r="J596" s="1"/>
+    </row>
+    <row r="597" spans="1:10">
+      <c r="J597" s="1"/>
+    </row>
+    <row r="598" spans="1:10">
+      <c r="J598" s="1"/>
+    </row>
+    <row r="599" spans="1:10">
+      <c r="J599" s="1"/>
+    </row>
+    <row r="600" spans="1:10">
+      <c r="J600" s="1"/>
+    </row>
+    <row r="601" spans="1:10">
+      <c r="J601" s="1"/>
+    </row>
+    <row r="602" spans="1:10">
+      <c r="J602" s="1"/>
+    </row>
+    <row r="603" spans="1:10">
+      <c r="J603" s="1"/>
+    </row>
+    <row r="604" spans="1:10">
+      <c r="J604" s="1"/>
+    </row>
+    <row r="605" spans="1:10">
+      <c r="J605" s="1"/>
+    </row>
+    <row r="606" spans="1:10">
+      <c r="J606" s="1"/>
+    </row>
+    <row r="607" spans="1:10">
+      <c r="J607" s="1"/>
+    </row>
+    <row r="608" spans="1:10">
+      <c r="J608" s="1"/>
+    </row>
+    <row r="609" spans="1:10">
+      <c r="J609" s="1"/>
+    </row>
+    <row r="610" spans="1:10">
+      <c r="J610" s="1"/>
+    </row>
+    <row r="611" spans="1:10">
+      <c r="J611" s="1"/>
+    </row>
+    <row r="612" spans="1:10">
+      <c r="J612" s="1"/>
+    </row>
+    <row r="613" spans="1:10">
+      <c r="J613" s="1"/>
+    </row>
+    <row r="614" spans="1:10">
+      <c r="J614" s="1"/>
+    </row>
+    <row r="615" spans="1:10">
+      <c r="J615" s="1"/>
+    </row>
+    <row r="616" spans="1:10">
+      <c r="J616" s="1"/>
+    </row>
+    <row r="617" spans="1:10">
+      <c r="J617" s="1"/>
+    </row>
+    <row r="618" spans="1:10">
+      <c r="J618" s="1"/>
+    </row>
+    <row r="619" spans="1:10">
+      <c r="J619" s="1"/>
+    </row>
+    <row r="620" spans="1:10">
+      <c r="J620" s="1"/>
+    </row>
+    <row r="621" spans="1:10">
+      <c r="J621" s="1"/>
+    </row>
+    <row r="622" spans="1:10">
+      <c r="J622" s="1"/>
+    </row>
+    <row r="623" spans="1:10">
+      <c r="J623" s="1"/>
+    </row>
+    <row r="624" spans="1:10">
+      <c r="J624" s="1"/>
+    </row>
+    <row r="625" spans="1:10">
+      <c r="J625" s="1"/>
+    </row>
+    <row r="626" spans="1:10">
+      <c r="J626" s="1"/>
+    </row>
+    <row r="627" spans="1:10">
+      <c r="J627" s="1"/>
+    </row>
+    <row r="628" spans="1:10">
+      <c r="J628" s="1"/>
+    </row>
+    <row r="629" spans="1:10">
+      <c r="J629" s="1"/>
+    </row>
+    <row r="630" spans="1:10">
+      <c r="J630" s="1"/>
+    </row>
+    <row r="631" spans="1:10">
+      <c r="J631" s="1"/>
+    </row>
+    <row r="632" spans="1:10">
+      <c r="J632" s="1"/>
+    </row>
+    <row r="633" spans="1:10">
+      <c r="J633" s="1"/>
+    </row>
+    <row r="634" spans="1:10">
+      <c r="J634" s="1"/>
+    </row>
+    <row r="635" spans="1:10">
+      <c r="J635" s="1"/>
+    </row>
+    <row r="636" spans="1:10">
+      <c r="J636" s="1"/>
+    </row>
+    <row r="637" spans="1:10">
+      <c r="J637" s="1"/>
+    </row>
+    <row r="638" spans="1:10">
+      <c r="J638" s="1"/>
+    </row>
+    <row r="639" spans="1:10">
+      <c r="J639" s="1"/>
+    </row>
+    <row r="640" spans="1:10">
+      <c r="J640" s="1"/>
+    </row>
+    <row r="641" spans="1:10">
+      <c r="J641" s="1"/>
+    </row>
+    <row r="642" spans="1:10">
+      <c r="J642" s="1"/>
+    </row>
+    <row r="643" spans="1:10">
+      <c r="J643" s="1"/>
+    </row>
+    <row r="644" spans="1:10">
+      <c r="J644" s="1"/>
+    </row>
+    <row r="645" spans="1:10">
+      <c r="J645" s="1"/>
+    </row>
+    <row r="646" spans="1:10">
+      <c r="J646" s="1"/>
+    </row>
+    <row r="647" spans="1:10">
+      <c r="J647" s="1"/>
+    </row>
+    <row r="648" spans="1:10">
+      <c r="J648" s="1"/>
+    </row>
+    <row r="649" spans="1:10">
+      <c r="J649" s="1"/>
+    </row>
+    <row r="650" spans="1:10">
+      <c r="J650" s="1"/>
+    </row>
+    <row r="651" spans="1:10">
+      <c r="J651" s="1"/>
+    </row>
+    <row r="652" spans="1:10">
+      <c r="J652" s="1"/>
+    </row>
+    <row r="653" spans="1:10">
+      <c r="J653" s="1"/>
+    </row>
+    <row r="654" spans="1:10">
+      <c r="J654" s="1"/>
+    </row>
+    <row r="655" spans="1:10">
+      <c r="J655" s="1"/>
+    </row>
+    <row r="656" spans="1:10">
+      <c r="J656" s="1"/>
+    </row>
+    <row r="657" spans="1:10">
+      <c r="J657" s="1"/>
+    </row>
+    <row r="658" spans="1:10">
+      <c r="J658" s="1"/>
+    </row>
+    <row r="659" spans="1:10">
+      <c r="J659" s="1"/>
+    </row>
+    <row r="660" spans="1:10">
+      <c r="J660" s="1"/>
+    </row>
+    <row r="661" spans="1:10">
+      <c r="J661" s="1"/>
+    </row>
+    <row r="662" spans="1:10">
+      <c r="J662" s="1"/>
+    </row>
+    <row r="663" spans="1:10">
+      <c r="J663" s="1"/>
+    </row>
+    <row r="664" spans="1:10">
+      <c r="J664" s="1"/>
+    </row>
+    <row r="665" spans="1:10">
+      <c r="J665" s="1"/>
+    </row>
+    <row r="666" spans="1:10">
+      <c r="J666" s="1"/>
+    </row>
+    <row r="667" spans="1:10">
+      <c r="J667" s="1"/>
+    </row>
+    <row r="668" spans="1:10">
+      <c r="J668" s="1"/>
+    </row>
+    <row r="669" spans="1:10">
+      <c r="J669" s="1"/>
+    </row>
+    <row r="670" spans="1:10">
+      <c r="J670" s="1"/>
+    </row>
+    <row r="671" spans="1:10">
+      <c r="J671" s="1"/>
+    </row>
+    <row r="672" spans="1:10">
+      <c r="J672" s="1"/>
+    </row>
+    <row r="673" spans="1:10">
+      <c r="J673" s="1"/>
+    </row>
+    <row r="674" spans="1:10">
+      <c r="J674" s="1"/>
+    </row>
+    <row r="675" spans="1:10">
+      <c r="J675" s="1"/>
+    </row>
+    <row r="676" spans="1:10">
+      <c r="J676" s="1"/>
+    </row>
+    <row r="677" spans="1:10">
+      <c r="J677" s="1"/>
+    </row>
+    <row r="678" spans="1:10">
+      <c r="J678" s="1"/>
+    </row>
+    <row r="679" spans="1:10">
+      <c r="J679" s="1"/>
+    </row>
+    <row r="680" spans="1:10">
+      <c r="J680" s="1"/>
+    </row>
+    <row r="681" spans="1:10">
+      <c r="J681" s="1"/>
+    </row>
+    <row r="682" spans="1:10">
+      <c r="J682" s="1"/>
+    </row>
+    <row r="683" spans="1:10">
+      <c r="J683" s="1"/>
+    </row>
+    <row r="684" spans="1:10">
+      <c r="J684" s="1"/>
+    </row>
+    <row r="685" spans="1:10">
+      <c r="J685" s="1"/>
+    </row>
+    <row r="686" spans="1:10">
+      <c r="J686" s="1"/>
+    </row>
+    <row r="687" spans="1:10">
+      <c r="J687" s="1"/>
+    </row>
+    <row r="688" spans="1:10">
+      <c r="J688" s="1"/>
+    </row>
+    <row r="689" spans="1:10">
+      <c r="J689" s="1"/>
+    </row>
+    <row r="690" spans="1:10">
+      <c r="J690" s="1"/>
+    </row>
+    <row r="691" spans="1:10">
+      <c r="J691" s="1"/>
+    </row>
+    <row r="692" spans="1:10">
+      <c r="J692" s="1"/>
+    </row>
+    <row r="693" spans="1:10">
+      <c r="J693" s="1"/>
+    </row>
+    <row r="694" spans="1:10">
+      <c r="J694" s="1"/>
+    </row>
+    <row r="695" spans="1:10">
+      <c r="J695" s="1"/>
+    </row>
+    <row r="696" spans="1:10">
+      <c r="J696" s="1"/>
+    </row>
+    <row r="697" spans="1:10">
+      <c r="J697" s="1"/>
+    </row>
+    <row r="698" spans="1:10">
+      <c r="J698" s="1"/>
+    </row>
+    <row r="699" spans="1:10">
+      <c r="J699" s="1"/>
+    </row>
+    <row r="700" spans="1:10">
+      <c r="J700" s="1"/>
+    </row>
+    <row r="701" spans="1:10">
+      <c r="J701" s="1"/>
+    </row>
+    <row r="702" spans="1:10">
+      <c r="J702" s="1"/>
+    </row>
+    <row r="703" spans="1:10">
+      <c r="J703" s="1"/>
+    </row>
+    <row r="704" spans="1:10">
+      <c r="J704" s="1"/>
+    </row>
+    <row r="705" spans="1:10">
+      <c r="J705" s="1"/>
+    </row>
+    <row r="706" spans="1:10">
+      <c r="J706" s="1"/>
+    </row>
+    <row r="707" spans="1:10">
+      <c r="J707" s="1"/>
+    </row>
+    <row r="708" spans="1:10">
+      <c r="J708" s="1"/>
+    </row>
+    <row r="709" spans="1:10">
+      <c r="J709" s="1"/>
+    </row>
+    <row r="710" spans="1:10">
+      <c r="J710" s="1"/>
+    </row>
+    <row r="711" spans="1:10">
+      <c r="J711" s="1"/>
+    </row>
+    <row r="712" spans="1:10">
+      <c r="J712" s="1"/>
+    </row>
+    <row r="713" spans="1:10">
+      <c r="J713" s="1"/>
+    </row>
+    <row r="714" spans="1:10">
+      <c r="J714" s="1"/>
+    </row>
+    <row r="715" spans="1:10">
+      <c r="J715" s="1"/>
+    </row>
+    <row r="716" spans="1:10">
+      <c r="J716" s="1"/>
+    </row>
+    <row r="717" spans="1:10">
+      <c r="J717" s="1"/>
+    </row>
+    <row r="718" spans="1:10">
+      <c r="J718" s="1"/>
+    </row>
+    <row r="719" spans="1:10">
+      <c r="J719" s="1"/>
+    </row>
+    <row r="720" spans="1:10">
+      <c r="J720" s="1"/>
+    </row>
+    <row r="721" spans="1:10">
+      <c r="J721" s="1"/>
+    </row>
+    <row r="722" spans="1:10">
+      <c r="J722" s="1"/>
+    </row>
+    <row r="723" spans="1:10">
+      <c r="J723" s="1"/>
+    </row>
+    <row r="724" spans="1:10">
+      <c r="J724" s="1"/>
+    </row>
+    <row r="725" spans="1:10">
+      <c r="J725" s="1"/>
+    </row>
+    <row r="726" spans="1:10">
+      <c r="J726" s="1"/>
+    </row>
+    <row r="727" spans="1:10">
+      <c r="J727" s="1"/>
+    </row>
+    <row r="728" spans="1:10">
+      <c r="J728" s="1"/>
+    </row>
+    <row r="729" spans="1:10">
+      <c r="J729" s="1"/>
+    </row>
+    <row r="730" spans="1:10">
+      <c r="J730" s="1"/>
+    </row>
+    <row r="731" spans="1:10">
+      <c r="J731" s="1"/>
+    </row>
+    <row r="732" spans="1:10">
+      <c r="J732" s="1"/>
+    </row>
+    <row r="733" spans="1:10">
+      <c r="J733" s="1"/>
+    </row>
+    <row r="734" spans="1:10">
+      <c r="J734" s="1"/>
+    </row>
+    <row r="735" spans="1:10">
+      <c r="J735" s="1"/>
+    </row>
+    <row r="736" spans="1:10">
+      <c r="J736" s="1"/>
+    </row>
+    <row r="737" spans="1:10">
+      <c r="J737" s="1"/>
+    </row>
+    <row r="738" spans="1:10">
+      <c r="J738" s="1"/>
+    </row>
+    <row r="739" spans="1:10">
+      <c r="J739" s="1"/>
+    </row>
+    <row r="740" spans="1:10">
+      <c r="J740" s="1"/>
+    </row>
+    <row r="741" spans="1:10">
+      <c r="J741" s="1"/>
+    </row>
+    <row r="742" spans="1:10">
+      <c r="J742" s="1"/>
+    </row>
+    <row r="743" spans="1:10">
+      <c r="J743" s="1"/>
+    </row>
+    <row r="744" spans="1:10">
+      <c r="J744" s="1"/>
+    </row>
+    <row r="745" spans="1:10">
+      <c r="J745" s="1"/>
+    </row>
+    <row r="746" spans="1:10">
+      <c r="J746" s="1"/>
+    </row>
+    <row r="747" spans="1:10">
+      <c r="J747" s="1"/>
+    </row>
+    <row r="748" spans="1:10">
+      <c r="J748" s="1"/>
+    </row>
+    <row r="749" spans="1:10">
+      <c r="J749" s="1"/>
+    </row>
+    <row r="750" spans="1:10">
+      <c r="J750" s="1"/>
+    </row>
+    <row r="751" spans="1:10">
+      <c r="J751" s="1"/>
+    </row>
+    <row r="752" spans="1:10">
+      <c r="J752" s="1"/>
+    </row>
+    <row r="753" spans="1:10">
+      <c r="J753" s="1"/>
+    </row>
+    <row r="754" spans="1:10">
+      <c r="J754" s="1"/>
+    </row>
+    <row r="755" spans="1:10">
+      <c r="J755" s="1"/>
+    </row>
+    <row r="756" spans="1:10">
+      <c r="J756" s="1"/>
+    </row>
+    <row r="757" spans="1:10">
+      <c r="J757" s="1"/>
+    </row>
+    <row r="758" spans="1:10">
+      <c r="J758" s="1"/>
+    </row>
+    <row r="759" spans="1:10">
+      <c r="J759" s="1"/>
+    </row>
+    <row r="760" spans="1:10">
+      <c r="J760" s="1"/>
+    </row>
+    <row r="761" spans="1:10">
+      <c r="J761" s="1"/>
+    </row>
+    <row r="762" spans="1:10">
+      <c r="J762" s="1"/>
+    </row>
+    <row r="763" spans="1:10">
+      <c r="J763" s="1"/>
+    </row>
+    <row r="764" spans="1:10">
+      <c r="J764" s="1"/>
+    </row>
+    <row r="765" spans="1:10">
+      <c r="J765" s="1"/>
+    </row>
+    <row r="766" spans="1:10">
+      <c r="J766" s="1"/>
+    </row>
+    <row r="767" spans="1:10">
+      <c r="J767" s="1"/>
+    </row>
+    <row r="768" spans="1:10">
+      <c r="J768" s="1"/>
+    </row>
+    <row r="769" spans="1:10">
+      <c r="J769" s="1"/>
+    </row>
+    <row r="770" spans="1:10">
+      <c r="J770" s="1"/>
+    </row>
+    <row r="771" spans="1:10">
+      <c r="J771" s="1"/>
+    </row>
+    <row r="772" spans="1:10">
+      <c r="J772" s="1"/>
+    </row>
+    <row r="773" spans="1:10">
+      <c r="J773" s="1"/>
+    </row>
+    <row r="774" spans="1:10">
+      <c r="J774" s="1"/>
+    </row>
+    <row r="775" spans="1:10">
+      <c r="J775" s="1"/>
+    </row>
+    <row r="776" spans="1:10">
+      <c r="J776" s="1"/>
+    </row>
+    <row r="777" spans="1:10">
+      <c r="J777" s="1"/>
+    </row>
+    <row r="778" spans="1:10">
+      <c r="J778" s="1"/>
+    </row>
+    <row r="779" spans="1:10">
+      <c r="J779" s="1"/>
+    </row>
+    <row r="780" spans="1:10">
+      <c r="J780" s="1"/>
+    </row>
+    <row r="781" spans="1:10">
+      <c r="J781" s="1"/>
+    </row>
+    <row r="782" spans="1:10">
+      <c r="J782" s="1"/>
+    </row>
+    <row r="783" spans="1:10">
+      <c r="J783" s="1"/>
+    </row>
+    <row r="784" spans="1:10">
+      <c r="J784" s="1"/>
+    </row>
+    <row r="785" spans="1:10">
+      <c r="J785" s="1"/>
+    </row>
+    <row r="786" spans="1:10">
+      <c r="J786" s="1"/>
+    </row>
+    <row r="787" spans="1:10">
+      <c r="J787" s="1"/>
+    </row>
+    <row r="788" spans="1:10">
+      <c r="J788" s="1"/>
+    </row>
+    <row r="789" spans="1:10">
+      <c r="J789" s="1"/>
+    </row>
+    <row r="790" spans="1:10">
+      <c r="J790" s="1"/>
+    </row>
+    <row r="791" spans="1:10">
+      <c r="J791" s="1"/>
+    </row>
+    <row r="792" spans="1:10">
+      <c r="J792" s="1"/>
+    </row>
+    <row r="793" spans="1:10">
+      <c r="J793" s="1"/>
+    </row>
+    <row r="794" spans="1:10">
+      <c r="J794" s="1"/>
+    </row>
+    <row r="795" spans="1:10">
+      <c r="J795" s="1"/>
+    </row>
+    <row r="796" spans="1:10">
+      <c r="J796" s="1"/>
+    </row>
+    <row r="797" spans="1:10">
+      <c r="J797" s="1"/>
+    </row>
+    <row r="798" spans="1:10">
+      <c r="J798" s="1"/>
+    </row>
+    <row r="799" spans="1:10">
+      <c r="J799" s="1"/>
+    </row>
+    <row r="800" spans="1:10">
+      <c r="J800" s="1"/>
+    </row>
+    <row r="801" spans="1:10">
+      <c r="J801" s="1"/>
+    </row>
+    <row r="802" spans="1:10">
+      <c r="J802" s="1"/>
+    </row>
+    <row r="803" spans="1:10">
+      <c r="J803" s="1"/>
+    </row>
+    <row r="804" spans="1:10">
+      <c r="J804" s="1"/>
+    </row>
+    <row r="805" spans="1:10">
+      <c r="J805" s="1"/>
+    </row>
+    <row r="806" spans="1:10">
+      <c r="J806" s="1"/>
+    </row>
+    <row r="807" spans="1:10">
+      <c r="J807" s="1"/>
+    </row>
+    <row r="808" spans="1:10">
+      <c r="J808" s="1"/>
+    </row>
+    <row r="809" spans="1:10">
+      <c r="J809" s="1"/>
+    </row>
+    <row r="810" spans="1:10">
+      <c r="J810" s="1"/>
+    </row>
+    <row r="811" spans="1:10">
+      <c r="J811" s="1"/>
+    </row>
+    <row r="812" spans="1:10">
+      <c r="J812" s="1"/>
+    </row>
+    <row r="813" spans="1:10">
+      <c r="J813" s="1"/>
+    </row>
+    <row r="814" spans="1:10">
+      <c r="J814" s="1"/>
+    </row>
+    <row r="815" spans="1:10">
+      <c r="J815" s="1"/>
+    </row>
+    <row r="816" spans="1:10">
+      <c r="J816" s="1"/>
+    </row>
+    <row r="817" spans="1:10">
+      <c r="J817" s="1"/>
+    </row>
+    <row r="818" spans="1:10">
+      <c r="J818" s="1"/>
+    </row>
+    <row r="819" spans="1:10">
+      <c r="J819" s="1"/>
+    </row>
+    <row r="820" spans="1:10">
+      <c r="J820" s="1"/>
+    </row>
+    <row r="821" spans="1:10">
+      <c r="J821" s="1"/>
+    </row>
+    <row r="822" spans="1:10">
+      <c r="J822" s="1"/>
+    </row>
+    <row r="823" spans="1:10">
+      <c r="J823" s="1"/>
+    </row>
+    <row r="824" spans="1:10">
+      <c r="J824" s="1"/>
+    </row>
+    <row r="825" spans="1:10">
+      <c r="J825" s="1"/>
+    </row>
+    <row r="826" spans="1:10">
+      <c r="J826" s="1"/>
+    </row>
+    <row r="827" spans="1:10">
+      <c r="J827" s="1"/>
+    </row>
+    <row r="828" spans="1:10">
+      <c r="J828" s="1"/>
+    </row>
+    <row r="829" spans="1:10">
+      <c r="J829" s="1"/>
+    </row>
+    <row r="830" spans="1:10">
+      <c r="J830" s="1"/>
+    </row>
+    <row r="831" spans="1:10">
+      <c r="J831" s="1"/>
+    </row>
+    <row r="832" spans="1:10">
+      <c r="J832" s="1"/>
+    </row>
+    <row r="833" spans="1:10">
+      <c r="J833" s="1"/>
+    </row>
+    <row r="834" spans="1:10">
+      <c r="J834" s="1"/>
+    </row>
+    <row r="835" spans="1:10">
+      <c r="J835" s="1"/>
+    </row>
+    <row r="836" spans="1:10">
+      <c r="J836" s="1"/>
+    </row>
+    <row r="837" spans="1:10">
+      <c r="J837" s="1"/>
+    </row>
+    <row r="838" spans="1:10">
+      <c r="J838" s="1"/>
+    </row>
+    <row r="839" spans="1:10">
+      <c r="J839" s="1"/>
+    </row>
+    <row r="840" spans="1:10">
+      <c r="J840" s="1"/>
+    </row>
+    <row r="841" spans="1:10">
+      <c r="J841" s="1"/>
+    </row>
+    <row r="842" spans="1:10">
+      <c r="J842" s="1"/>
+    </row>
+    <row r="843" spans="1:10">
+      <c r="J843" s="1"/>
+    </row>
+    <row r="844" spans="1:10">
+      <c r="J844" s="1"/>
+    </row>
+    <row r="845" spans="1:10">
+      <c r="J845" s="1"/>
+    </row>
+    <row r="846" spans="1:10">
+      <c r="J846" s="1"/>
+    </row>
+    <row r="847" spans="1:10">
+      <c r="J847" s="1"/>
+    </row>
+    <row r="848" spans="1:10">
+      <c r="J848" s="1"/>
+    </row>
+    <row r="849" spans="1:10">
+      <c r="J849" s="1"/>
+    </row>
+    <row r="850" spans="1:10">
+      <c r="J850" s="1"/>
+    </row>
+    <row r="851" spans="1:10">
+      <c r="J851" s="1"/>
+    </row>
+    <row r="852" spans="1:10">
+      <c r="J852" s="1"/>
+    </row>
+    <row r="853" spans="1:10">
+      <c r="J853" s="1"/>
+    </row>
+    <row r="854" spans="1:10">
+      <c r="J854" s="1"/>
+    </row>
+    <row r="855" spans="1:10">
+      <c r="J855" s="1"/>
+    </row>
+    <row r="856" spans="1:10">
+      <c r="J856" s="1"/>
+    </row>
+    <row r="857" spans="1:10">
+      <c r="J857" s="1"/>
+    </row>
+    <row r="858" spans="1:10">
+      <c r="J858" s="1"/>
+    </row>
+    <row r="859" spans="1:10">
+      <c r="J859" s="1"/>
+    </row>
+    <row r="860" spans="1:10">
+      <c r="J860" s="1"/>
+    </row>
+    <row r="861" spans="1:10">
+      <c r="J861" s="1"/>
+    </row>
+    <row r="862" spans="1:10">
+      <c r="J862" s="1"/>
+    </row>
+    <row r="863" spans="1:10">
+      <c r="J863" s="1"/>
+    </row>
+    <row r="864" spans="1:10">
+      <c r="J864" s="1"/>
+    </row>
+    <row r="865" spans="1:10">
+      <c r="J865" s="1"/>
+    </row>
+    <row r="866" spans="1:10">
+      <c r="J866" s="1"/>
+    </row>
+    <row r="867" spans="1:10">
+      <c r="J867" s="1"/>
+    </row>
+    <row r="868" spans="1:10">
+      <c r="J868" s="1"/>
+    </row>
+    <row r="869" spans="1:10">
+      <c r="J869" s="1"/>
+    </row>
+    <row r="870" spans="1:10">
+      <c r="J870" s="1"/>
+    </row>
+    <row r="871" spans="1:10">
+      <c r="J871" s="1"/>
+    </row>
+    <row r="872" spans="1:10">
+      <c r="J872" s="1"/>
+    </row>
+    <row r="873" spans="1:10">
+      <c r="J873" s="1"/>
+    </row>
+    <row r="874" spans="1:10">
+      <c r="J874" s="1"/>
+    </row>
+    <row r="875" spans="1:10">
+      <c r="J875" s="1"/>
+    </row>
+    <row r="876" spans="1:10">
+      <c r="J876" s="1"/>
+    </row>
+    <row r="877" spans="1:10">
+      <c r="J877" s="1"/>
+    </row>
+    <row r="878" spans="1:10">
+      <c r="J878" s="1"/>
+    </row>
+    <row r="879" spans="1:10">
+      <c r="J879" s="1"/>
+    </row>
+    <row r="880" spans="1:10">
+      <c r="J880" s="1"/>
+    </row>
+    <row r="881" spans="1:10">
+      <c r="J881" s="1"/>
+    </row>
+    <row r="882" spans="1:10">
+      <c r="J882" s="1"/>
+    </row>
+    <row r="883" spans="1:10">
+      <c r="J883" s="1"/>
+    </row>
+    <row r="884" spans="1:10">
+      <c r="J884" s="1"/>
+    </row>
+    <row r="885" spans="1:10">
+      <c r="J885" s="1"/>
+    </row>
+    <row r="886" spans="1:10">
+      <c r="J886" s="1"/>
+    </row>
+    <row r="887" spans="1:10">
+      <c r="J887" s="1"/>
+    </row>
+    <row r="888" spans="1:10">
+      <c r="J888" s="1"/>
+    </row>
+    <row r="889" spans="1:10">
+      <c r="J889" s="1"/>
+    </row>
+    <row r="890" spans="1:10">
+      <c r="J890" s="1"/>
+    </row>
+    <row r="891" spans="1:10">
+      <c r="J891" s="1"/>
+    </row>
+    <row r="892" spans="1:10">
+      <c r="J892" s="1"/>
+    </row>
+    <row r="893" spans="1:10">
+      <c r="J893" s="1"/>
+    </row>
+    <row r="894" spans="1:10">
+      <c r="J894" s="1"/>
+    </row>
+    <row r="895" spans="1:10">
+      <c r="J895" s="1"/>
+    </row>
+    <row r="896" spans="1:10">
+      <c r="J896" s="1"/>
+    </row>
+    <row r="897" spans="1:10">
+      <c r="J897" s="1"/>
+    </row>
+    <row r="898" spans="1:10">
+      <c r="J898" s="1"/>
+    </row>
+    <row r="899" spans="1:10">
+      <c r="J899" s="1"/>
+    </row>
+    <row r="900" spans="1:10">
+      <c r="J900" s="1"/>
+    </row>
+    <row r="901" spans="1:10">
+      <c r="J901" s="1"/>
+    </row>
+    <row r="902" spans="1:10">
+      <c r="J902" s="1"/>
+    </row>
+    <row r="903" spans="1:10">
+      <c r="J903" s="1"/>
+    </row>
+    <row r="904" spans="1:10">
+      <c r="J904" s="1"/>
+    </row>
+    <row r="905" spans="1:10">
+      <c r="J905" s="1"/>
+    </row>
+    <row r="906" spans="1:10">
+      <c r="J906" s="1"/>
+    </row>
+    <row r="907" spans="1:10">
+      <c r="J907" s="1"/>
+    </row>
+    <row r="908" spans="1:10">
+      <c r="J908" s="1"/>
+    </row>
+    <row r="909" spans="1:10">
+      <c r="J909" s="1"/>
+    </row>
+    <row r="910" spans="1:10">
+      <c r="J910" s="1"/>
+    </row>
+    <row r="911" spans="1:10">
+      <c r="J911" s="1"/>
+    </row>
+    <row r="912" spans="1:10">
+      <c r="J912" s="1"/>
+    </row>
+    <row r="913" spans="1:10">
+      <c r="J913" s="1"/>
+    </row>
+    <row r="914" spans="1:10">
+      <c r="J914" s="1"/>
+    </row>
+    <row r="915" spans="1:10">
+      <c r="J915" s="1"/>
+    </row>
+    <row r="916" spans="1:10">
+      <c r="J916" s="1"/>
+    </row>
+    <row r="917" spans="1:10">
+      <c r="J917" s="1"/>
+    </row>
+    <row r="918" spans="1:10">
+      <c r="J918" s="1"/>
+    </row>
+    <row r="919" spans="1:10">
+      <c r="J919" s="1"/>
+    </row>
+    <row r="920" spans="1:10">
+      <c r="J920" s="1"/>
+    </row>
+    <row r="921" spans="1:10">
+      <c r="J921" s="1"/>
+    </row>
+    <row r="922" spans="1:10">
+      <c r="J922" s="1"/>
+    </row>
+    <row r="923" spans="1:10">
+      <c r="J923" s="1"/>
+    </row>
+    <row r="924" spans="1:10">
+      <c r="J924" s="1"/>
+    </row>
+    <row r="925" spans="1:10">
+      <c r="J925" s="1"/>
+    </row>
+    <row r="926" spans="1:10">
+      <c r="J926" s="1"/>
+    </row>
+    <row r="927" spans="1:10">
+      <c r="J927" s="1"/>
+    </row>
+    <row r="928" spans="1:10">
+      <c r="J928" s="1"/>
+    </row>
+    <row r="929" spans="1:10">
+      <c r="J929" s="1"/>
+    </row>
+    <row r="930" spans="1:10">
+      <c r="J930" s="1"/>
+    </row>
+    <row r="931" spans="1:10">
+      <c r="J931" s="1"/>
+    </row>
+    <row r="932" spans="1:10">
+      <c r="J932" s="1"/>
+    </row>
+    <row r="933" spans="1:10">
+      <c r="J933" s="1"/>
+    </row>
+    <row r="934" spans="1:10">
+      <c r="J934" s="1"/>
+    </row>
+    <row r="935" spans="1:10">
+      <c r="J935" s="1"/>
+    </row>
+    <row r="936" spans="1:10">
+      <c r="J936" s="1"/>
+    </row>
+    <row r="937" spans="1:10">
+      <c r="J937" s="1"/>
+    </row>
+    <row r="938" spans="1:10">
+      <c r="J938" s="1"/>
+    </row>
+    <row r="939" spans="1:10">
+      <c r="J939" s="1"/>
+    </row>
+    <row r="940" spans="1:10">
+      <c r="J940" s="1"/>
+    </row>
+    <row r="941" spans="1:10">
+      <c r="J941" s="1"/>
+    </row>
+    <row r="942" spans="1:10">
+      <c r="J942" s="1"/>
+    </row>
+    <row r="943" spans="1:10">
+      <c r="J943" s="1"/>
+    </row>
+    <row r="944" spans="1:10">
+      <c r="J944" s="1"/>
+    </row>
+    <row r="945" spans="1:10">
+      <c r="J945" s="1"/>
+    </row>
+    <row r="946" spans="1:10">
+      <c r="J946" s="1"/>
+    </row>
+    <row r="947" spans="1:10">
+      <c r="J947" s="1"/>
+    </row>
+    <row r="948" spans="1:10">
+      <c r="J948" s="1"/>
+    </row>
+    <row r="949" spans="1:10">
+      <c r="J949" s="1"/>
+    </row>
+    <row r="950" spans="1:10">
+      <c r="J950" s="1"/>
+    </row>
+    <row r="951" spans="1:10">
+      <c r="J951" s="1"/>
+    </row>
+    <row r="952" spans="1:10">
+      <c r="J952" s="1"/>
+    </row>
+    <row r="953" spans="1:10">
+      <c r="J953" s="1"/>
+    </row>
+    <row r="954" spans="1:10">
+      <c r="J954" s="1"/>
+    </row>
+    <row r="955" spans="1:10">
+      <c r="J955" s="1"/>
+    </row>
+    <row r="956" spans="1:10">
+      <c r="J956" s="1"/>
+    </row>
+    <row r="957" spans="1:10">
+      <c r="J957" s="1"/>
+    </row>
+    <row r="958" spans="1:10">
+      <c r="J958" s="1"/>
+    </row>
+    <row r="959" spans="1:10">
+      <c r="J959" s="1"/>
+    </row>
+    <row r="960" spans="1:10">
+      <c r="J960" s="1"/>
+    </row>
+    <row r="961" spans="1:10">
+      <c r="J961" s="1"/>
+    </row>
+    <row r="962" spans="1:10">
+      <c r="J962" s="1"/>
+    </row>
+    <row r="963" spans="1:10">
+      <c r="J963" s="1"/>
+    </row>
+    <row r="964" spans="1:10">
+      <c r="J964" s="1"/>
+    </row>
+    <row r="965" spans="1:10">
+      <c r="J965" s="1"/>
+    </row>
+    <row r="966" spans="1:10">
+      <c r="J966" s="1"/>
+    </row>
+    <row r="967" spans="1:10">
+      <c r="J967" s="1"/>
+    </row>
+    <row r="968" spans="1:10">
+      <c r="J968" s="1"/>
+    </row>
+    <row r="969" spans="1:10">
+      <c r="J969" s="1"/>
+    </row>
+    <row r="970" spans="1:10">
+      <c r="J970" s="1"/>
+    </row>
+    <row r="971" spans="1:10">
+      <c r="J971" s="1"/>
+    </row>
+    <row r="972" spans="1:10">
+      <c r="J972" s="1"/>
+    </row>
+    <row r="973" spans="1:10">
+      <c r="J973" s="1"/>
+    </row>
+    <row r="974" spans="1:10">
+      <c r="J974" s="1"/>
+    </row>
+    <row r="975" spans="1:10">
+      <c r="J975" s="1"/>
+    </row>
+    <row r="976" spans="1:10">
+      <c r="J976" s="1"/>
+    </row>
+    <row r="977" spans="1:10">
+      <c r="J977" s="1"/>
+    </row>
+    <row r="978" spans="1:10">
+      <c r="J978" s="1"/>
+    </row>
+    <row r="979" spans="1:10">
+      <c r="J979" s="1"/>
+    </row>
+    <row r="980" spans="1:10">
+      <c r="J980" s="1"/>
+    </row>
+    <row r="981" spans="1:10">
+      <c r="J981" s="1"/>
+    </row>
+    <row r="982" spans="1:10">
+      <c r="J982" s="1"/>
+    </row>
+    <row r="983" spans="1:10">
+      <c r="J983" s="1"/>
+    </row>
+    <row r="984" spans="1:10">
+      <c r="J984" s="1"/>
+    </row>
+    <row r="985" spans="1:10">
+      <c r="J985" s="1"/>
+    </row>
+    <row r="986" spans="1:10">
+      <c r="J986" s="1"/>
+    </row>
+    <row r="987" spans="1:10">
+      <c r="J987" s="1"/>
+    </row>
+    <row r="988" spans="1:10">
+      <c r="J988" s="1"/>
+    </row>
+    <row r="989" spans="1:10">
+      <c r="J989" s="1"/>
+    </row>
+    <row r="990" spans="1:10">
+      <c r="J990" s="1"/>
+    </row>
+    <row r="991" spans="1:10">
+      <c r="J991" s="1"/>
+    </row>
+    <row r="992" spans="1:10">
+      <c r="J992" s="1"/>
+    </row>
+    <row r="993" spans="1:10">
+      <c r="J993" s="1"/>
+    </row>
+    <row r="994" spans="1:10">
+      <c r="J994" s="1"/>
+    </row>
+    <row r="995" spans="1:10">
+      <c r="J995" s="1"/>
+    </row>
+    <row r="996" spans="1:10">
+      <c r="J996" s="1"/>
+    </row>
+    <row r="997" spans="1:10">
+      <c r="J997" s="1"/>
+    </row>
+    <row r="998" spans="1:10">
+      <c r="J998" s="1"/>
+    </row>
+    <row r="999" spans="1:10">
+      <c r="J999" s="1"/>
+    </row>
+    <row r="1000" spans="1:10">
+      <c r="J1000" s="1"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.511805555555555" right="0.511805555555555" top="0.7875" bottom="0.7875" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.51180555555555" right="0.51180555555555" top="0.7875" bottom="0.7875" header="0.51180555555555" footer="0.51180555555555"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
     <oddHeader/>
     <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
   <drawing r:id="rId1"/>
+  <tableParts count="0"/>
 </worksheet>
 </file>